--- a/desktop/templates/uzag-vidomist.xlsx
+++ b/desktop/templates/uzag-vidomist.xlsx
@@ -811,11 +811,7 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="52" t="inlineStr">
-        <is>
-          <t>взводу матеріального забезпечення 2 батальйону безпілотних систем</t>
-        </is>
-      </c>
+      <c r="A5" s="52"/>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="52" t="inlineStr">
@@ -865,16 +861,10 @@
         </is>
       </c>
       <c r="D8" s="56" t="n"/>
-      <c r="E8" s="46" t="inlineStr">
-        <is>
-          <t>25.07.2026 по 25.08.2026</t>
-        </is>
-      </c>
+      <c r="E8" s="46"/>
       <c r="F8" s="57" t="n"/>
       <c r="G8" s="56" t="n"/>
-      <c r="H8" s="47" t="n">
-        <v>46259</v>
-      </c>
+      <c r="H8" s="47"/>
       <c r="I8" s="57" t="n"/>
       <c r="J8" s="56" t="n"/>
     </row>
@@ -955,423 +945,171 @@
       </c>
     </row>
     <row r="12" ht="15.6" customHeight="1">
-      <c r="A12" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B12" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Блендер Braun MultiQuick 5245 WH </t>
-        </is>
-      </c>
+      <c r="A12" s="10"/>
+      <c r="B12" s="39"/>
       <c r="C12" s="57" t="n"/>
       <c r="D12" s="56" t="n"/>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F12" s="30" t="n">
-        <v>2899</v>
-      </c>
-      <c r="G12" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="13" t="n">
-        <v>1</v>
-      </c>
+      <c r="E12" s="11"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="13"/>
       <c r="J12" s="14" t="n"/>
     </row>
     <row r="13" ht="15.6" customHeight="1">
-      <c r="A13" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="B13" s="39" t="inlineStr">
-        <is>
-          <t>Термос ТВН-12</t>
-        </is>
-      </c>
+      <c r="A13" s="10"/>
+      <c r="B13" s="39"/>
       <c r="C13" s="57" t="n"/>
       <c r="D13" s="56" t="n"/>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>к-т</t>
-        </is>
-      </c>
-      <c r="F13" s="11" t="n">
-        <v>83418.5</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>29</v>
-      </c>
-      <c r="H13" s="13" t="n">
-        <v>29</v>
-      </c>
-      <c r="I13" s="13" t="n">
-        <v>29</v>
-      </c>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
       <c r="J13" s="15" t="n"/>
     </row>
     <row r="14" ht="15.6" customHeight="1">
-      <c r="A14" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="B14" s="39" t="inlineStr">
-        <is>
-          <t>Термос ТН-36</t>
-        </is>
-      </c>
+      <c r="A14" s="10"/>
+      <c r="B14" s="39"/>
       <c r="C14" s="57" t="n"/>
       <c r="D14" s="56" t="n"/>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
-          <t>к-т</t>
-        </is>
-      </c>
-      <c r="F14" s="11" t="n">
-        <v>28997.28</v>
-      </c>
-      <c r="G14" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="H14" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="I14" s="13" t="n">
-        <v>6</v>
-      </c>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
       <c r="J14" s="15" t="n"/>
     </row>
     <row r="15" ht="15.6" customHeight="1">
-      <c r="A15" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="B15" s="39" t="inlineStr">
-        <is>
-          <t>Термос ТН-36</t>
-        </is>
-      </c>
+      <c r="A15" s="10"/>
+      <c r="B15" s="39"/>
       <c r="C15" s="57" t="n"/>
       <c r="D15" s="56" t="n"/>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>к-т</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>3681.9</v>
-      </c>
-      <c r="G15" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="13" t="n">
-        <v>1</v>
-      </c>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
       <c r="J15" s="15" t="n"/>
     </row>
     <row r="16" ht="15.6" customHeight="1">
-      <c r="A16" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="B16" s="39" t="inlineStr">
-        <is>
-          <t>Цистерна для води ЦВ-4</t>
-        </is>
-      </c>
+      <c r="A16" s="10"/>
+      <c r="B16" s="39"/>
       <c r="C16" s="57" t="n"/>
       <c r="D16" s="56" t="n"/>
-      <c r="E16" s="11" t="inlineStr">
-        <is>
-          <t>к-т</t>
-        </is>
-      </c>
-      <c r="F16" s="11" t="n">
-        <v>7041.67</v>
-      </c>
-      <c r="G16" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="13" t="n">
-        <v>1</v>
-      </c>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
       <c r="J16" s="15" t="n"/>
     </row>
     <row r="17" ht="15.6" customHeight="1">
-      <c r="A17" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="B17" s="39" t="inlineStr">
-        <is>
-          <t>Причіп-цистерна для води ЦВ-1,2, 1990 р.в.</t>
-        </is>
-      </c>
+      <c r="A17" s="10"/>
+      <c r="B17" s="39"/>
       <c r="C17" s="57" t="n"/>
       <c r="D17" s="56" t="n"/>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>к-т</t>
-        </is>
-      </c>
-      <c r="F17" s="11" t="n">
-        <v>21336.22</v>
-      </c>
-      <c r="G17" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="13" t="n">
-        <v>1</v>
-      </c>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
       <c r="J17" s="15" t="n"/>
     </row>
     <row r="18" ht="25.8" customHeight="1">
-      <c r="A18" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="B18" s="41" t="inlineStr">
-        <is>
-          <t>ПАРОКОНВЕКТОМАТ APACH AP10QT в комплекті з фільтром</t>
-        </is>
-      </c>
+      <c r="A18" s="10"/>
+      <c r="B18" s="41"/>
       <c r="C18" s="57" t="n"/>
       <c r="D18" s="56" t="n"/>
-      <c r="E18" s="11" t="inlineStr">
-        <is>
-          <t>к-т</t>
-        </is>
-      </c>
-      <c r="F18" s="11" t="n">
-        <v>203820</v>
-      </c>
-      <c r="G18" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="13" t="n">
-        <v>1</v>
-      </c>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
       <c r="J18" s="15" t="n"/>
     </row>
     <row r="19" ht="29.4" customHeight="1">
-      <c r="A19" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B19" s="41" t="inlineStr">
-        <is>
-          <t>СКОВОРОДА ЕЛЕКТРИЧНА ПРОМИСЛОВА СЕМ-0,2 ЭТАЛОН</t>
-        </is>
-      </c>
+      <c r="A19" s="10"/>
+      <c r="B19" s="41"/>
       <c r="C19" s="57" t="n"/>
       <c r="D19" s="56" t="n"/>
-      <c r="E19" s="11" t="inlineStr">
-        <is>
-          <t>к-т</t>
-        </is>
-      </c>
-      <c r="F19" s="11" t="n">
-        <v>37962</v>
-      </c>
-      <c r="G19" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" s="13" t="n">
-        <v>1</v>
-      </c>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
       <c r="J19" s="15" t="n"/>
     </row>
     <row r="20" ht="15.6" customHeight="1">
-      <c r="A20" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B20" s="39" t="inlineStr">
-        <is>
-          <t>СЛАЙСЕР HURAKAN HKN-HM250. 250 мм</t>
-        </is>
-      </c>
+      <c r="A20" s="10"/>
+      <c r="B20" s="39"/>
       <c r="C20" s="57" t="n"/>
       <c r="D20" s="56" t="n"/>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>к-т</t>
-        </is>
-      </c>
-      <c r="F20" s="11" t="n">
-        <v>20230</v>
-      </c>
-      <c r="G20" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="13" t="n">
-        <v>1</v>
-      </c>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
       <c r="J20" s="15" t="n"/>
     </row>
     <row r="21" ht="32.4" customHeight="1">
-      <c r="A21" s="10" t="n">
-        <v>10</v>
-      </c>
-      <c r="B21" s="35" t="inlineStr">
-        <is>
-          <t>ПЛИТА ІНДУКЦІЙНА 2-КОНФОРОЧНА HURAKAN HKN-ICF70D2V 7000W</t>
-        </is>
-      </c>
+      <c r="A21" s="10"/>
+      <c r="B21" s="35"/>
       <c r="C21" s="57" t="n"/>
       <c r="D21" s="56" t="n"/>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>к-т</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="n">
-        <v>16509.6</v>
-      </c>
-      <c r="G21" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="18" t="n">
-        <v>1</v>
-      </c>
+      <c r="E21" s="16"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
       <c r="J21" s="15" t="n"/>
     </row>
     <row r="22" ht="15.6" customHeight="1">
-      <c r="A22" s="10" t="n">
-        <v>11</v>
-      </c>
-      <c r="B22" s="40" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Кухня КП 130-11</t>
-        </is>
-      </c>
+      <c r="A22" s="10"/>
+      <c r="B22" s="40"/>
       <c r="C22" s="57" t="n"/>
       <c r="D22" s="56" t="n"/>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>к-т</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="n">
-        <v>234377.22</v>
-      </c>
-      <c r="G22" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H22" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="I22" s="18" t="n">
-        <v>3</v>
-      </c>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
       <c r="J22" s="15" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="B23" s="35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ящик для зберігання STRATA з колесами чорний 145 л, 450х940х520 </t>
-        </is>
-      </c>
+      <c r="A23" s="10"/>
+      <c r="B23" s="35"/>
       <c r="C23" s="57" t="n"/>
       <c r="D23" s="56" t="n"/>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>к-т</t>
-        </is>
-      </c>
-      <c r="F23" s="19" t="n">
-        <v>10395</v>
-      </c>
-      <c r="G23" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="H23" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="I23" s="18" t="n">
-        <v>6</v>
-      </c>
+      <c r="E23" s="16"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
       <c r="J23" s="15" t="n"/>
     </row>
     <row r="24" ht="26.4" customHeight="1">
-      <c r="A24" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="B24" s="35" t="inlineStr">
-        <is>
-          <t>Дегідратор професійний харчовий Tekhniko DH-12S-SS</t>
-        </is>
-      </c>
+      <c r="A24" s="10"/>
+      <c r="B24" s="35"/>
       <c r="C24" s="57" t="n"/>
       <c r="D24" s="56" t="n"/>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F24" s="19" t="n">
-        <v>11000</v>
-      </c>
-      <c r="G24" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" s="18" t="n">
-        <v>1</v>
-      </c>
+      <c r="E24" s="16"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
       <c r="J24" s="15" t="n"/>
     </row>
     <row r="25" ht="17.4" customHeight="1">
-      <c r="A25" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="B25" s="35" t="inlineStr">
-        <is>
-          <t>Вакуумний пакувальник Rommelsbacher VAC 285</t>
-        </is>
-      </c>
+      <c r="A25" s="10"/>
+      <c r="B25" s="35"/>
       <c r="C25" s="57" t="n"/>
       <c r="D25" s="56" t="n"/>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F25" s="19" t="n">
-        <v>5425</v>
-      </c>
-      <c r="G25" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="18" t="n">
-        <v>1</v>
-      </c>
+      <c r="E25" s="16"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
       <c r="J25" s="15" t="n"/>
     </row>
     <row r="26" ht="16.5" customHeight="1">
@@ -1411,11 +1149,7 @@
       <c r="F27" s="31" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="27" t="inlineStr">
-        <is>
-          <t>Реквізити книги обліку військового майна №14, реєстраційний номер ______ за номенклатурою на 2026 рік.</t>
-        </is>
-      </c>
+      <c r="A28" s="27"/>
       <c r="B28" s="21" t="n"/>
       <c r="C28" s="21" t="n"/>
       <c r="D28" s="26" t="n"/>
@@ -1444,11 +1178,7 @@
       <c r="G30" s="23" t="n"/>
       <c r="H30" s="23" t="n"/>
       <c r="I30" s="23" t="n"/>
-      <c r="J30" s="29" t="inlineStr">
-        <is>
-          <t>Сергій ОГОРОДНИК</t>
-        </is>
-      </c>
+      <c r="J30" s="29"/>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="36" t="inlineStr">
